--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29520,7 +29520,7 @@
     </row>
     <row r="1065">
       <c r="A1065" s="1" t="n">
-        <v>45940.6380555556</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1065" t="n">
         <v>265000</v>
@@ -29541,6 +29541,32 @@
         <v>243</v>
       </c>
       <c r="H1065" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="1" t="n">
+        <v>45943.6494212963</v>
+      </c>
+      <c r="B1066" t="n">
+        <v>116000</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1066" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29546,7 +29546,7 @@
     </row>
     <row r="1066">
       <c r="A1066" s="1" t="n">
-        <v>45943.6494212963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1066" t="n">
         <v>116000</v>
@@ -29567,6 +29567,32 @@
         <v>262</v>
       </c>
       <c r="H1066" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="1" t="n">
+        <v>45944.6494328704</v>
+      </c>
+      <c r="B1067" t="n">
+        <v>199000</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1067" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1518,6 +1518,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.17499995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00499999523163</t>
   </si>
 </sst>
 </file>
@@ -29572,7 +29575,7 @@
     </row>
     <row r="1067">
       <c r="A1067" s="1" t="n">
-        <v>45944.6494328704</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1067" t="n">
         <v>199000</v>
@@ -29593,6 +29596,32 @@
         <v>257</v>
       </c>
       <c r="H1067" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="1" t="n">
+        <v>45945.6496296296</v>
+      </c>
+      <c r="B1068" t="n">
+        <v>59000</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1068" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1521,6 +1521,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.00499999523163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0349999666214</t>
   </si>
 </sst>
 </file>
@@ -29601,7 +29604,7 @@
     </row>
     <row r="1068">
       <c r="A1068" s="1" t="n">
-        <v>45945.6496296296</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1068" t="n">
         <v>59000</v>
@@ -29610,7 +29613,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="D1068" t="n">
-        <v>1.00999999046326</v>
+        <v>1.00499999523163</v>
       </c>
       <c r="E1068" t="n">
         <v>1.04499995708466</v>
@@ -29622,6 +29625,32 @@
         <v>502</v>
       </c>
       <c r="H1068" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="1" t="n">
+        <v>45946.6493402778</v>
+      </c>
+      <c r="B1069" t="n">
+        <v>179000</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>503</v>
+      </c>
+      <c r="H1069" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29630,7 +29630,7 @@
     </row>
     <row r="1069">
       <c r="A1069" s="1" t="n">
-        <v>45946.6493402778</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1069" t="n">
         <v>179000</v>
@@ -29651,6 +29651,32 @@
         <v>503</v>
       </c>
       <c r="H1069" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="1" t="n">
+        <v>45947.6495833333</v>
+      </c>
+      <c r="B1070" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>0.991999983787537</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1070" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1524,6 +1524,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.0349999666214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06500005722046</t>
   </si>
 </sst>
 </file>
@@ -29656,7 +29659,7 @@
     </row>
     <row r="1070">
       <c r="A1070" s="1" t="n">
-        <v>45947.6495833333</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1070" t="n">
         <v>158000</v>
@@ -29677,6 +29680,32 @@
         <v>259</v>
       </c>
       <c r="H1070" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="1" t="n">
+        <v>45950.6496296296</v>
+      </c>
+      <c r="B1071" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>1.06500005722046</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1071" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29685,7 +29685,7 @@
     </row>
     <row r="1071">
       <c r="A1071" s="1" t="n">
-        <v>45950.6496296296</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1071" t="n">
         <v>90000</v>
@@ -29706,6 +29706,32 @@
         <v>504</v>
       </c>
       <c r="H1071" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="1" t="n">
+        <v>45951.6190625</v>
+      </c>
+      <c r="B1072" t="n">
+        <v>67000</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1072" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29711,7 +29711,7 @@
     </row>
     <row r="1072">
       <c r="A1072" s="1" t="n">
-        <v>45951.6190625</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1072" t="n">
         <v>67000</v>
@@ -29732,6 +29732,32 @@
         <v>240</v>
       </c>
       <c r="H1072" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="1" t="n">
+        <v>45952.6421527778</v>
+      </c>
+      <c r="B1073" t="n">
+        <v>57000</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>1.0349999666214</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G1073" t="s">
+        <v>249</v>
+      </c>
+      <c r="H1073" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29737,7 +29737,7 @@
     </row>
     <row r="1073">
       <c r="A1073" s="1" t="n">
-        <v>45952.6421527778</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1073" t="n">
         <v>57000</v>
@@ -29758,6 +29758,32 @@
         <v>249</v>
       </c>
       <c r="H1073" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="1" t="n">
+        <v>45953.6295949074</v>
+      </c>
+      <c r="B1074" t="n">
+        <v>69000</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1074" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29763,7 +29763,7 @@
     </row>
     <row r="1074">
       <c r="A1074" s="1" t="n">
-        <v>45953.6295949074</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1074" t="n">
         <v>69000</v>
@@ -29784,6 +29784,32 @@
         <v>377</v>
       </c>
       <c r="H1074" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>45954.6495949074</v>
+      </c>
+      <c r="B1075" t="n">
+        <v>67000</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>378</v>
+      </c>
+      <c r="H1075" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29789,7 +29789,7 @@
     </row>
     <row r="1075">
       <c r="A1075" s="1" t="n">
-        <v>45954.6495949074</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1075" t="n">
         <v>67000</v>
@@ -29810,6 +29810,32 @@
         <v>378</v>
       </c>
       <c r="H1075" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>45957.6910763889</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>103000</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>257</v>
+      </c>
+      <c r="H1076" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29815,7 +29815,7 @@
     </row>
     <row r="1076">
       <c r="A1076" s="1" t="n">
-        <v>45957.6910763889</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1076" t="n">
         <v>103000</v>
@@ -29836,6 +29836,32 @@
         <v>257</v>
       </c>
       <c r="H1076" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>45958.6910069444</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>1.04499995708466</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>378</v>
+      </c>
+      <c r="H1077" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29841,7 +29841,7 @@
     </row>
     <row r="1077">
       <c r="A1077" s="1" t="n">
-        <v>45958.6910069444</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1077" t="n">
         <v>26000</v>
@@ -29862,6 +29862,32 @@
         <v>378</v>
       </c>
       <c r="H1077" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>45959.6912037037</v>
+      </c>
+      <c r="B1078" t="n">
+        <v>93000</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>0.987999975681305</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1078" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29867,7 +29867,7 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>45959.6912037037</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1078" t="n">
         <v>93000</v>
@@ -29888,6 +29888,32 @@
         <v>259</v>
       </c>
       <c r="H1078" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>45960.4264351852</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1079" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29893,7 +29893,7 @@
     </row>
     <row r="1079">
       <c r="A1079" s="1" t="n">
-        <v>45960.4264351852</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1079" t="n">
         <v>18000</v>
@@ -29914,6 +29914,32 @@
         <v>264</v>
       </c>
       <c r="H1079" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="1" t="n">
+        <v>45961.6805787037</v>
+      </c>
+      <c r="B1080" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1080" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29919,7 +29919,7 @@
     </row>
     <row r="1080">
       <c r="A1080" s="1" t="n">
-        <v>45961.6805787037</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1080" t="n">
         <v>46000</v>
@@ -29940,6 +29940,32 @@
         <v>379</v>
       </c>
       <c r="H1080" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="1" t="n">
+        <v>45964.6482986111</v>
+      </c>
+      <c r="B1081" t="n">
+        <v>49000</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>1.01499998569489</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1081" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29945,7 +29945,7 @@
     </row>
     <row r="1081">
       <c r="A1081" s="1" t="n">
-        <v>45964.6482986111</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1081" t="n">
         <v>49000</v>
@@ -29966,6 +29966,32 @@
         <v>386</v>
       </c>
       <c r="H1081" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>45965.6911689815</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>380</v>
+      </c>
+      <c r="H1082" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29971,7 +29971,7 @@
     </row>
     <row r="1082">
       <c r="A1082" s="1" t="n">
-        <v>45965.6911689815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1082" t="n">
         <v>10000</v>
@@ -29992,6 +29992,32 @@
         <v>380</v>
       </c>
       <c r="H1082" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>45966.5495601852</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>380</v>
+      </c>
+      <c r="H1083" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29997,25 +29997,25 @@
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>45966.5495601852</v>
+        <v>45967.6868402778</v>
       </c>
       <c r="B1083" t="n">
-        <v>12000</v>
+        <v>56000</v>
       </c>
       <c r="C1083" t="n">
         <v>1.02999997138977</v>
       </c>
       <c r="D1083" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="E1083" t="n">
         <v>1.00999999046326</v>
       </c>
-      <c r="E1083" t="n">
-        <v>1.01999998092651</v>
-      </c>
       <c r="F1083" t="n">
-        <v>1.02499997615814</v>
+        <v>1.00499999523163</v>
       </c>
       <c r="G1083" t="s">
-        <v>380</v>
+        <v>502</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29997,25 +29997,25 @@
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>45967.6868402778</v>
+        <v>45968.6721990741</v>
       </c>
       <c r="B1083" t="n">
-        <v>56000</v>
+        <v>93000</v>
       </c>
       <c r="C1083" t="n">
-        <v>1.02999997138977</v>
+        <v>1.00499999523163</v>
       </c>
       <c r="D1083" t="n">
-        <v>0.998000025749207</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="E1083" t="n">
-        <v>1.00999999046326</v>
+        <v>1.00499999523163</v>
       </c>
       <c r="F1083" t="n">
-        <v>1.00499999523163</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="G1083" t="s">
-        <v>502</v>
+        <v>394</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -29997,27 +29997,105 @@
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>45968.6721990741</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1083" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>1.02499997615814</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>380</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>56000</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>0.998000025749207</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>1.00499999523163</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1085" t="n">
         <v>93000</v>
       </c>
-      <c r="C1083" t="n">
+      <c r="C1085" t="n">
         <v>1.00499999523163</v>
       </c>
-      <c r="D1083" t="n">
+      <c r="D1085" t="n">
         <v>0.949999988079071</v>
       </c>
-      <c r="E1083" t="n">
+      <c r="E1085" t="n">
         <v>1.00499999523163</v>
       </c>
-      <c r="F1083" t="n">
+      <c r="F1085" t="n">
         <v>0.959999978542328</v>
       </c>
-      <c r="G1083" t="s">
+      <c r="G1085" t="s">
         <v>394</v>
       </c>
-      <c r="H1083" t="s">
+      <c r="H1085" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>45971.6849421296</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>0.958000004291534</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>413</v>
+      </c>
+      <c r="H1086" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30075,7 +30075,7 @@
     </row>
     <row r="1086">
       <c r="A1086" s="1" t="n">
-        <v>45971.6849421296</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B1086" t="n">
         <v>158000</v>
@@ -30096,6 +30096,32 @@
         <v>413</v>
       </c>
       <c r="H1086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>45972.6911458333</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>0.888000011444092</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30101,7 +30101,7 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>45972.6911458333</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1087" t="n">
         <v>46000</v>
@@ -30122,6 +30122,32 @@
         <v>400</v>
       </c>
       <c r="H1087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>45973.6912152778</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>197000</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>0.917999982833862</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>484</v>
+      </c>
+      <c r="H1088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30127,7 +30127,7 @@
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>45973.6912152778</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1088" t="n">
         <v>197000</v>
@@ -30148,6 +30148,32 @@
         <v>484</v>
       </c>
       <c r="H1088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
+        <v>45974.6911226852</v>
+      </c>
+      <c r="B1089" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>0.885999977588654</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>0.86599999666214</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>488</v>
+      </c>
+      <c r="H1089" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30153,7 +30153,7 @@
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>45974.6911226852</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1089" t="n">
         <v>31000</v>
@@ -30162,7 +30162,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="D1089" t="n">
-        <v>0.86599999666214</v>
+        <v>0.864000022411346</v>
       </c>
       <c r="E1089" t="n">
         <v>0.870000004768372</v>
@@ -30174,6 +30174,32 @@
         <v>488</v>
       </c>
       <c r="H1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>45975.6909953704</v>
+      </c>
+      <c r="B1090" t="n">
+        <v>493000</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>0.772000014781952</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>0.851999998092651</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>423</v>
+      </c>
+      <c r="H1090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30179,7 +30179,7 @@
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>45975.6909953704</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1090" t="n">
         <v>493000</v>
@@ -30200,6 +30200,32 @@
         <v>423</v>
       </c>
       <c r="H1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>45978.6562384259</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>128000</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>0.818000018596649</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>422</v>
+      </c>
+      <c r="H1091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30205,7 +30205,7 @@
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>45978.6562384259</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1091" t="n">
         <v>128000</v>
@@ -30226,6 +30226,32 @@
         <v>422</v>
       </c>
       <c r="H1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>45979.6786921296</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>182000</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>0.837999999523163</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>423</v>
+      </c>
+      <c r="H1092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1527,6 +1527,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.06500005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.808000028133392</t>
   </si>
 </sst>
 </file>
@@ -30231,7 +30234,7 @@
     </row>
     <row r="1092">
       <c r="A1092" s="1" t="n">
-        <v>45979.6786921296</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1092" t="n">
         <v>182000</v>
@@ -30252,6 +30255,32 @@
         <v>423</v>
       </c>
       <c r="H1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>45980.6910416667</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>505</v>
+      </c>
+      <c r="H1093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30260,7 +30260,7 @@
     </row>
     <row r="1093">
       <c r="A1093" s="1" t="n">
-        <v>45980.6910416667</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1093" t="n">
         <v>40000</v>
@@ -30281,6 +30281,32 @@
         <v>505</v>
       </c>
       <c r="H1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>45981.6910648148</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>59000</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>0.78600001335144</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30286,7 +30286,7 @@
     </row>
     <row r="1094">
       <c r="A1094" s="1" t="n">
-        <v>45981.6910648148</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1094" t="n">
         <v>59000</v>
@@ -30307,6 +30307,32 @@
         <v>448</v>
       </c>
       <c r="H1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>45982.6759953704</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>0.78600001335144</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>422</v>
+      </c>
+      <c r="H1095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30312,7 +30312,7 @@
     </row>
     <row r="1095">
       <c r="A1095" s="1" t="n">
-        <v>45982.6759953704</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1095" t="n">
         <v>37000</v>
@@ -30333,6 +30333,32 @@
         <v>422</v>
       </c>
       <c r="H1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>45985.4213888889</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>424</v>
+      </c>
+      <c r="H1096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30338,7 +30338,7 @@
     </row>
     <row r="1096">
       <c r="A1096" s="1" t="n">
-        <v>45985.4213888889</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1096" t="n">
         <v>8000</v>
@@ -30359,6 +30359,32 @@
         <v>424</v>
       </c>
       <c r="H1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>45986.69125</v>
+      </c>
+      <c r="B1097" t="n">
+        <v>406000</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>0.878000020980835</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1097" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30364,7 +30364,7 @@
     </row>
     <row r="1097">
       <c r="A1097" s="1" t="n">
-        <v>45986.69125</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1097" t="n">
         <v>406000</v>
@@ -30385,6 +30385,32 @@
         <v>455</v>
       </c>
       <c r="H1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="1" t="n">
+        <v>45987.6910300926</v>
+      </c>
+      <c r="B1098" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>0.828000009059906</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1098" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30390,7 +30390,7 @@
     </row>
     <row r="1098">
       <c r="A1098" s="1" t="n">
-        <v>45987.6910300926</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1098" t="n">
         <v>213000</v>
@@ -30411,6 +30411,32 @@
         <v>448</v>
       </c>
       <c r="H1098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>45988.6772222222</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>146000</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30416,7 +30416,7 @@
     </row>
     <row r="1099">
       <c r="A1099" s="1" t="n">
-        <v>45988.6772222222</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1099" t="n">
         <v>146000</v>
@@ -30437,6 +30437,32 @@
         <v>455</v>
       </c>
       <c r="H1099" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>45989.6353587963</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>49000</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1100" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30442,7 +30442,7 @@
     </row>
     <row r="1100">
       <c r="A1100" s="1" t="n">
-        <v>45989.6353587963</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1100" t="n">
         <v>49000</v>
@@ -30463,6 +30463,32 @@
         <v>433</v>
       </c>
       <c r="H1100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="1" t="n">
+        <v>45992.657662037</v>
+      </c>
+      <c r="B1101" t="n">
+        <v>77000</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>0.78600001335144</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>422</v>
+      </c>
+      <c r="H1101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30468,7 +30468,7 @@
     </row>
     <row r="1101">
       <c r="A1101" s="1" t="n">
-        <v>45992.657662037</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1101" t="n">
         <v>77000</v>
@@ -30489,6 +30489,32 @@
         <v>422</v>
       </c>
       <c r="H1101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="1" t="n">
+        <v>45993.6761689815</v>
+      </c>
+      <c r="B1102" t="n">
+        <v>59000</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>477</v>
+      </c>
+      <c r="H1102" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30494,7 +30494,7 @@
     </row>
     <row r="1102">
       <c r="A1102" s="1" t="n">
-        <v>45993.6761689815</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1102" t="n">
         <v>59000</v>
@@ -30515,6 +30515,32 @@
         <v>477</v>
       </c>
       <c r="H1102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>45994.6335763889</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>0.797999978065491</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>0.779999971389771</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>475</v>
+      </c>
+      <c r="H1103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30520,7 +30520,7 @@
     </row>
     <row r="1103">
       <c r="A1103" s="1" t="n">
-        <v>45994.6335763889</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1103" t="n">
         <v>45000</v>
@@ -30541,6 +30541,32 @@
         <v>475</v>
       </c>
       <c r="H1103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>45995.6515509259</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>37000</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>0.773999989032745</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>475</v>
+      </c>
+      <c r="H1104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30546,7 +30546,7 @@
     </row>
     <row r="1104">
       <c r="A1104" s="1" t="n">
-        <v>45995.6515509259</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1104" t="n">
         <v>37000</v>
@@ -30567,6 +30567,32 @@
         <v>475</v>
       </c>
       <c r="H1104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>45996.6874537037</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1105" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30572,7 +30572,7 @@
     </row>
     <row r="1105">
       <c r="A1105" s="1" t="n">
-        <v>45996.6874537037</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B1105" t="n">
         <v>20000</v>
@@ -30593,6 +30593,32 @@
         <v>455</v>
       </c>
       <c r="H1105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>45999.6494675926</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30598,7 +30598,7 @@
     </row>
     <row r="1106">
       <c r="A1106" s="1" t="n">
-        <v>45999.6494675926</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B1106" t="n">
         <v>6000</v>
@@ -30619,6 +30619,32 @@
         <v>433</v>
       </c>
       <c r="H1106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>46000.6117476852</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30624,7 +30624,7 @@
     </row>
     <row r="1107">
       <c r="A1107" s="1" t="n">
-        <v>46000.6117476852</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B1107" t="n">
         <v>31000</v>
@@ -30645,6 +30645,32 @@
         <v>433</v>
       </c>
       <c r="H1107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="1" t="n">
+        <v>46001.6363888889</v>
+      </c>
+      <c r="B1108" t="n">
+        <v>72000</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>0.782000005245209</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1108" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30650,7 +30650,7 @@
     </row>
     <row r="1108">
       <c r="A1108" s="1" t="n">
-        <v>46001.6363888889</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B1108" t="n">
         <v>72000</v>
@@ -30671,6 +30671,32 @@
         <v>421</v>
       </c>
       <c r="H1108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="1" t="n">
+        <v>46002.664224537</v>
+      </c>
+      <c r="B1109" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>0.825999975204468</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>0.796000003814697</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>0.811999976634979</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1109" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30676,7 +30676,7 @@
     </row>
     <row r="1109">
       <c r="A1109" s="1" t="n">
-        <v>46002.664224537</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B1109" t="n">
         <v>35000</v>
@@ -30697,6 +30697,32 @@
         <v>421</v>
       </c>
       <c r="H1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>46003.6053819444</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1110" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30702,7 +30702,7 @@
     </row>
     <row r="1110">
       <c r="A1110" s="1" t="n">
-        <v>46003.6053819444</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1110" t="n">
         <v>20000</v>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30726,6 +30726,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>46006.3333333333</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30752,6 +30752,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>46007.3333333333</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>0.814000010490417</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>505</v>
+      </c>
+      <c r="H1112" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30778,6 +30778,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>46008.3333333333</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1113" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30804,6 +30804,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" s="1" t="n">
+        <v>46009.3333333333</v>
+      </c>
+      <c r="B1114" t="n">
+        <v>26000</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>0.790000021457672</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1114" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/UBM.MI.xlsx
+++ b/data/UBM.MI.xlsx
@@ -30830,6 +30830,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1115">
+      <c r="A1115" s="1" t="n">
+        <v>46010.3333333333</v>
+      </c>
+      <c r="B1115" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>0.804000020027161</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>0.783999979496002</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>0.794000029563904</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>475</v>
+      </c>
+      <c r="H1115" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
